--- a/AAII_Financials/Yearly/PHAR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PHAR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>PHAR</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,137 +656,149 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43831</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>297200</v>
+      </c>
+      <c r="E8" s="3">
         <v>245300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>205600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>198900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>212200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>189400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>154700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>107600</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E9" s="3">
         <v>25200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>17600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>21100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>23500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>23900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>25400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14900</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>261800</v>
+      </c>
+      <c r="E10" s="3">
         <v>220100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>188100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>177700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>188600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>165500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>129300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>92700</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -798,35 +810,39 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>83200</v>
+      </c>
+      <c r="E12" s="3">
         <v>68700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>52500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>65400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>38500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>32600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>33100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>22400</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -851,63 +867,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="3">
         <v>-15400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-6700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>8000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>24300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>62600</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E15" s="3">
         <v>6500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4000</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -916,62 +941,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>305800</v>
+      </c>
+      <c r="E17" s="3">
         <v>267100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>195300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>174900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>135900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>122000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>111200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>81300</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-21800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>24000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>76300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>67400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>43500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>26300</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -983,143 +1015,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E20" s="3">
         <v>3400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-15400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>18900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>44200</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-18700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>45800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>63600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>71900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>46100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-13900</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E22" s="3">
         <v>6000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>13400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>16400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>22400</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>15000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>23100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>44100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>52300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-102900</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-27600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-11300</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1144,63 +1192,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>37700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>40600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>28600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-91600</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>13700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>37800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>40600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>28600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-91500</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1225,9 +1282,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1252,9 +1312,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1279,9 +1342,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1306,63 +1372,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>15400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-18900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-44200</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>13700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>16000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>37700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>40600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>28600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-91600</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1387,68 +1462,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>13700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>16000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>37700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>40600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>28600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-91600</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43831</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1460,8 +1544,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1473,44 +1558,48 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E41" s="3">
         <v>61700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>207300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>191900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>205200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>74300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>92000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>70400</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>112900</v>
+      </c>
+      <c r="E42" s="3">
         <v>151700</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -1526,63 +1615,72 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>55100</v>
+      </c>
+      <c r="E43" s="3">
         <v>42600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>27600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>31900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>28900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>18300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12200</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>55700</v>
+      </c>
+      <c r="E44" s="3">
         <v>56800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>42300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>27300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>21200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>16200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>19800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>22000</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
@@ -1607,117 +1705,132 @@
       <c r="J45" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K45" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>278700</v>
+      </c>
+      <c r="E46" s="3">
         <v>316300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>277500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>249400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>263200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>119400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>132200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>106000</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E47" s="3">
         <v>10400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6200</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K47" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E48" s="3">
         <v>33500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>39100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>33200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9900</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E49" s="3">
         <v>71300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>74900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>83600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>88600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>74600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>57500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>63700</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1742,9 +1855,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1769,9 +1885,12 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -1779,26 +1898,29 @@
         <v>1600</v>
       </c>
       <c r="E52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F52" s="3">
         <v>1300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4400</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1823,36 +1945,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>400800</v>
+      </c>
+      <c r="E54" s="3">
         <v>462900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>425800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>397300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>418500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>255900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>245600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>199600</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1864,8 +1992,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1877,143 +2006,159 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>66600</v>
+      </c>
+      <c r="E57" s="3">
         <v>16000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>40600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11300</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E58" s="3">
         <v>5400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>53300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>40600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>27200</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E59" s="3">
         <v>6200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>26000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>45500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>33500</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E60" s="3">
         <v>78000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>59700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>46800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>76800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>114300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>94600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>72900</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>105100</v>
+      </c>
+      <c r="E61" s="3">
         <v>166100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>161500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>157500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>158000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>42900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>71500</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2023,24 +2168,27 @@
       <c r="E62" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F62" s="3">
-        <v>200</v>
+      <c r="F62" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="G62" s="3">
         <v>200</v>
       </c>
       <c r="H62" s="3">
+        <v>200</v>
+      </c>
+      <c r="I62" s="3">
         <v>19400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>36700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>34000</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2065,9 +2213,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2092,9 +2243,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2119,36 +2273,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>178900</v>
+      </c>
+      <c r="E66" s="3">
         <v>244100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>221200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>204400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>235000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>138500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>174900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>180200</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2160,8 +2320,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2186,9 +2347,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2213,9 +2377,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2240,9 +2407,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2267,36 +2437,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-274900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-267300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-265200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-269800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-271000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-331800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-380100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-424500</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2321,9 +2497,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2348,9 +2527,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2375,36 +2557,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>221900</v>
+      </c>
+      <c r="E76" s="3">
         <v>218800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>204600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>192900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>183400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>117400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>70700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19300</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2429,68 +2617,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43831</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>13700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>16000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>37700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>40600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>28600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-91600</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2502,35 +2699,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E83" s="3">
         <v>5100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>700</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2555,9 +2756,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2582,9 +2786,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2609,9 +2816,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2636,9 +2846,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2663,36 +2876,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-17300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>22500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>37800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>83600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>74100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>46200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>45900</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2704,35 +2923,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1400</v>
+        <v>-800</v>
       </c>
       <c r="E91" s="3">
         <v>-1400</v>
       </c>
       <c r="F91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G91" s="3">
         <v>-10700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3900</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2757,9 +2980,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2784,36 +3010,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-129400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>5300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-28300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7300</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2825,8 +3057,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -2851,9 +3084,12 @@
       <c r="J96" s="3">
         <v>0</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2878,9 +3114,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2905,9 +3144,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2932,88 +3174,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-27900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>60700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-63500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-20600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3900</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E101" s="3">
         <v>2100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-7400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1300</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-145600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>15400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-13200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>130800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>24600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>33400</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PHAR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PHAR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
   <si>
     <t>PHAR</t>
   </si>
@@ -817,7 +817,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>83200</v>
+        <v>83100</v>
       </c>
       <c r="E12" s="3">
         <v>68700</v>
@@ -876,8 +876,8 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>38</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3">
         <v>-15400</v>
@@ -907,13 +907,13 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>16100</v>
+        <v>6800</v>
       </c>
       <c r="E15" s="3">
         <v>6500</v>
       </c>
       <c r="F15" s="3">
-        <v>5500</v>
+        <v>6800</v>
       </c>
       <c r="G15" s="3">
         <v>6400</v>
@@ -948,7 +948,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>305800</v>
+        <v>300800</v>
       </c>
       <c r="E17" s="3">
         <v>267100</v>
@@ -978,7 +978,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-8600</v>
+        <v>-3600</v>
       </c>
       <c r="E18" s="3">
         <v>-21800</v>
@@ -1022,7 +1022,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-3200</v>
+        <v>1000</v>
       </c>
       <c r="E20" s="3">
         <v>3400</v>
@@ -1052,13 +1052,13 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>10700</v>
+        <v>2200</v>
       </c>
       <c r="E21" s="3">
         <v>-18700</v>
       </c>
       <c r="F21" s="3">
-        <v>19100</v>
+        <v>20300</v>
       </c>
       <c r="G21" s="3">
         <v>45800</v>
@@ -1082,7 +1082,7 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>9900</v>
+        <v>8700</v>
       </c>
       <c r="E22" s="3">
         <v>6000</v>
@@ -1142,7 +1142,7 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="E24" s="3">
         <v>-1500</v>
@@ -1202,7 +1202,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-11000</v>
+        <v>-11800</v>
       </c>
       <c r="E26" s="3">
         <v>-10500</v>
@@ -1232,7 +1232,7 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-11000</v>
+        <v>-11800</v>
       </c>
       <c r="E27" s="3">
         <v>-10600</v>
@@ -1382,7 +1382,7 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>3200</v>
+        <v>-1000</v>
       </c>
       <c r="E32" s="3">
         <v>-3400</v>
@@ -1412,7 +1412,7 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>-11000</v>
+        <v>-11800</v>
       </c>
       <c r="E33" s="3">
         <v>-10500</v>
@@ -1472,7 +1472,7 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>-11000</v>
+        <v>-11800</v>
       </c>
       <c r="E35" s="3">
         <v>-10500</v>
@@ -1625,7 +1625,7 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>55100</v>
+        <v>50200</v>
       </c>
       <c r="E43" s="3">
         <v>42600</v>
@@ -1715,7 +1715,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>278700</v>
+        <v>278400</v>
       </c>
       <c r="E46" s="3">
         <v>316300</v>
@@ -1955,7 +1955,7 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>400800</v>
+        <v>400000</v>
       </c>
       <c r="E54" s="3">
         <v>462900</v>
@@ -2013,7 +2013,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>66600</v>
+        <v>10100</v>
       </c>
       <c r="E57" s="3">
         <v>16000</v>
@@ -2072,8 +2072,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>38</v>
+      <c r="D59" s="3">
+        <v>3300</v>
       </c>
       <c r="E59" s="3">
         <v>6200</v>
@@ -2447,10 +2447,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-274900</v>
+        <v>-287900</v>
       </c>
       <c r="E72" s="3">
-        <v>-267300</v>
+        <v>-265500</v>
       </c>
       <c r="F72" s="3">
         <v>-265200</v>
@@ -2567,7 +2567,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>221900</v>
+        <v>221100</v>
       </c>
       <c r="E76" s="3">
         <v>218800</v>
@@ -2662,7 +2662,7 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>-11000</v>
+        <v>-11800</v>
       </c>
       <c r="E81" s="3">
         <v>-10500</v>
@@ -2706,13 +2706,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>16100</v>
+        <v>4800</v>
       </c>
       <c r="E83" s="3">
         <v>5100</v>
       </c>
       <c r="F83" s="3">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="G83" s="3">
         <v>4900</v>

--- a/AAII_Financials/Yearly/PHAR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PHAR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>PHAR</t>
   </si>
@@ -656,149 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43831</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>376100</v>
+      </c>
+      <c r="E8" s="3">
         <v>297200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>245300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>205600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>198900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>212200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>189400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>154700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>107600</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E9" s="3">
         <v>35400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>25200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>21100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>23500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>23900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>25400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14900</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>330600</v>
+      </c>
+      <c r="E10" s="3">
         <v>261800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>220100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>188100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>177700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>188600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>165500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>129300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>92700</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -811,38 +823,42 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E12" s="3">
         <v>83100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>68700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>52500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>65400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>38500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>32600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>33100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22400</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -870,69 +886,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E14" s="3">
         <v>5000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-16400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-7900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>10300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>8000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>24300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>62600</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E15" s="3">
         <v>6800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4000</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -942,68 +967,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>343400</v>
+      </c>
+      <c r="E17" s="3">
         <v>300800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>267100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>195300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>174900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>135900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>122000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>111200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>81300</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-21800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>24000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>76300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>67400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>43500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>26300</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1016,158 +1048,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-15400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>18900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>44200</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E21" s="3">
         <v>7200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-19600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>45800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>63600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>71900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>46100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-13900</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E22" s="3">
         <v>8700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>13400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>16400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>22400</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>15000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>23100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>44100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>52300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-102900</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E24" s="3">
         <v>3300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-27600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-11300</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1195,69 +1243,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>16000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>37700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>40600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>28600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-91600</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>13700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>16000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>37800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>40600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>28600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-91500</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1285,9 +1342,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1315,9 +1375,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1345,9 +1408,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1375,69 +1441,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E32" s="3">
         <v>4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>15400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-18900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-44200</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>13700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>16000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>37700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>40600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>28600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-91600</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1465,74 +1540,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>13700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>16000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>37700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>40600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>28600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-91600</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43831</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1545,8 +1629,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1559,50 +1644,54 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>145300</v>
+      </c>
+      <c r="E41" s="3">
         <v>54900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>61700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>207300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>191900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>205200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>74300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>92000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>70400</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E42" s="3">
         <v>112900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>151700</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -1618,74 +1707,83 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E43" s="3">
         <v>50200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>42600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>25300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>27600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>31900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>28900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>18300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12200</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E44" s="3">
         <v>55700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>56800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>42300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>27300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>21200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>16200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>19800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>22000</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>38</v>
+      <c r="D45" s="3">
+        <v>0</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>38</v>
@@ -1708,129 +1806,144 @@
       <c r="K45" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>299500</v>
+      </c>
+      <c r="E46" s="3">
         <v>278400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>316300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>277500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>249400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>263200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>119400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>132200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>106000</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E47" s="3">
         <v>4200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6200</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E48" s="3">
         <v>24100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>33500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>39100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>33200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9900</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>135500</v>
+      </c>
+      <c r="E49" s="3">
         <v>61000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>71300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>74900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>83600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>88600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>74600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>57500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>63700</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1858,9 +1971,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1888,39 +2004,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="E52" s="3">
         <v>1600</v>
       </c>
       <c r="F52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G52" s="3">
         <v>1300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4400</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1948,39 +2070,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>500000</v>
+      </c>
+      <c r="E54" s="3">
         <v>400000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>462900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>425800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>397300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>418500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>255900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>245600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>199600</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1993,8 +2121,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2007,158 +2136,174 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E57" s="3">
         <v>10100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>40600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11300</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E58" s="3">
         <v>7200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>53300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>40600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>27200</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E59" s="3">
         <v>3300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>20300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>45500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>33500</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>115800</v>
+      </c>
+      <c r="E60" s="3">
         <v>73800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>78000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>59700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>46800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>76800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>114300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>94600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>72900</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>107100</v>
+      </c>
+      <c r="E61" s="3">
         <v>105100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>166100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>161500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>157500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>158000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>42900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>71500</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2171,24 +2316,27 @@
       <c r="F62" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G62" s="3">
-        <v>200</v>
+      <c r="G62" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="H62" s="3">
         <v>200</v>
       </c>
       <c r="I62" s="3">
+        <v>200</v>
+      </c>
+      <c r="J62" s="3">
         <v>19400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>36700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>34000</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2216,9 +2364,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2246,9 +2397,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2276,39 +2430,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>222900</v>
+      </c>
+      <c r="E66" s="3">
         <v>178900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>244100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>221200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>204400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>235000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>138500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>174900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>180200</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2321,8 +2481,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2350,9 +2511,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2380,9 +2544,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2410,9 +2577,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2440,39 +2610,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-258000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-287900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-265500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-265200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-269800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-271000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-331800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-380100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-424500</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2500,9 +2676,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2530,9 +2709,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2560,39 +2742,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>277100</v>
+      </c>
+      <c r="E76" s="3">
         <v>221100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>218800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>204600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>192900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>183400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>117400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>70700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19300</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2620,74 +2808,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43831</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>13700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>16000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>37700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>40600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>28600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-91600</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2700,38 +2897,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E83" s="3">
         <v>4800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>700</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2759,9 +2960,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2789,9 +2993,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2819,9 +3026,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2849,9 +3059,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2879,39 +3092,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>54700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-17300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>22500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>37800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>83600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>74100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>46200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>45900</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2924,38 +3143,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-1400</v>
       </c>
       <c r="F91" s="3">
         <v>-1400</v>
       </c>
       <c r="G91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H91" s="3">
         <v>-10700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3900</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2983,9 +3206,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3013,39 +3239,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E94" s="3">
         <v>31600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-129400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>5300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-28300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7300</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3058,8 +3290,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3087,9 +3320,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3117,9 +3353,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3147,9 +3386,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3177,97 +3419,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-34400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-27900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>60700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-63500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-20600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3900</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-7400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1300</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>90400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-145600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>15400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-13200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>130800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>24600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>33400</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
